--- a/projects/paper-02/03-screen/数据_4_全文下载追踪.xlsx
+++ b/projects/paper-02/03-screen/数据_4_全文下载追踪.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -85,8 +85,14 @@
     <font>
       <color rgb="009C0006"/>
     </font>
+    <font>
+      <color rgb="007D6608"/>
+    </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -134,6 +140,11 @@
         <fgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -147,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -192,6 +203,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -6376,25 +6393,17 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2021_Timing-specific associations between income-to-needs ratio and hippocampal and a.pdf</t>
-        </is>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>排除-E2</t>
+          <t>2021_Timing-specific associations between income-to-needs ratio and hippocampal.pdf</t>
+        </is>
+      </c>
+      <c r="I120" s="17" t="inlineStr">
+        <is>
+          <t>已下载</t>
         </is>
       </c>
       <c r="J120" s="2" t="n"/>
-      <c r="K120" s="6" t="inlineStr">
-        <is>
-          <t>排除-E2</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="inlineStr">
-        <is>
-          <t>主暴露为income-to-needs ratio，教育为协变量</t>
-        </is>
-      </c>
+      <c r="K120" s="6" t="n"/>
+      <c r="L120" s="2" t="n"/>
       <c r="M120" s="2" t="n"/>
     </row>
     <row r="121" ht="50" customHeight="1">
